--- a/main/ig/cm-oid-specialite-ordinale.xlsx
+++ b/main/ig/cm-oid-specialite-ordinale.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R38-SpecialiteOrdinale/FHIR/TRE-R38-SpecialiteOrdinale|1.5.0</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -417,7 +420,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>32</v>
@@ -429,7 +432,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
         <v>29</v>
